--- a/Data/RemapDrafts/DilucRemapDraft.xlsx
+++ b/Data/RemapDrafts/DilucRemapDraft.xlsx
@@ -1,24 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Computer\Games\Genshin\Repos\Repos\Fix-Raiden-Boss\Data\RemapDrafts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98505A20-525B-4585-A831-461D9C7B4692}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03D420CA-C2F9-4B35-BDC8-09A96F15F4A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{952D2824-24F3-4ADA-97F3-C3056522EE51}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="34620" windowHeight="13900" activeTab="1" xr2:uid="{952D2824-24F3-4ADA-97F3-C3056522EE51}"/>
   </bookViews>
   <sheets>
-    <sheet name="V4.0 - Diluc to DilucFlamme" sheetId="1" r:id="rId1"/>
-    <sheet name="V4.0 - DilucFlamme to Diluc" sheetId="2" r:id="rId2"/>
+    <sheet name="Credits" sheetId="3" r:id="rId1"/>
+    <sheet name="V4.0 - Diluc to DilucFlamme" sheetId="1" r:id="rId2"/>
+    <sheet name="V4.0 - DilucFlamme to Diluc" sheetId="2" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'V4.0 - Diluc to DilucFlamme'!$A$1:$D$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'V4.0 - DilucFlamme to Diluc'!$A$1:$D$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'V4.0 - Diluc to DilucFlamme'!$A$1:$D$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'V4.0 - DilucFlamme to Diluc'!$A$1:$D$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="66">
   <si>
     <t>Uncertainty</t>
   </si>
@@ -230,13 +231,22 @@
   </si>
   <si>
     <t>DilucFlamme's left wrist</t>
+  </si>
+  <si>
+    <t>Authors</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>AlbertGold#2696</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -247,6 +257,22 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="20"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -270,14 +296,18 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="2">
@@ -630,17 +660,48 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B83B636-BD46-4C60-AD13-409476CFBADC}">
+  <dimension ref="A1:A4"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="14.453125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" ht="26" x14ac:dyDescent="0.6">
+      <c r="A1" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A3" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
+        <v>65</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A4" r:id="rId1" xr:uid="{78FE207D-DCBD-4718-BFBC-82BABA581A35}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9C91934-8FCF-4990-8068-9FBE5A41A305}">
   <dimension ref="A1:D87"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.28515625" customWidth="1"/>
-    <col min="2" max="2" width="20.140625" customWidth="1"/>
+    <col min="1" max="1" width="13.26953125" customWidth="1"/>
+    <col min="2" max="2" width="20.1796875" customWidth="1"/>
     <col min="3" max="3" width="15" customWidth="1"/>
-    <col min="4" max="4" width="62.28515625" customWidth="1"/>
+    <col min="4" max="4" width="62.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
@@ -654,7 +715,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>0</v>
       </c>
@@ -665,7 +726,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>1</v>
       </c>
@@ -673,7 +734,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>2</v>
       </c>
@@ -684,7 +745,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>3</v>
       </c>
@@ -692,7 +753,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>4</v>
       </c>
@@ -700,7 +761,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>5</v>
       </c>
@@ -708,7 +769,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>6</v>
       </c>
@@ -722,7 +783,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>7</v>
       </c>
@@ -730,7 +791,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>8</v>
       </c>
@@ -738,7 +799,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>9</v>
       </c>
@@ -746,7 +807,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>10</v>
       </c>
@@ -754,7 +815,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>11</v>
       </c>
@@ -762,7 +823,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>12</v>
       </c>
@@ -776,7 +837,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>13</v>
       </c>
@@ -787,7 +848,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>14</v>
       </c>
@@ -798,7 +859,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>15</v>
       </c>
@@ -806,7 +867,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>16</v>
       </c>
@@ -814,7 +875,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>17</v>
       </c>
@@ -825,7 +886,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>18</v>
       </c>
@@ -836,7 +897,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>19</v>
       </c>
@@ -844,7 +905,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>20</v>
       </c>
@@ -852,7 +913,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>21</v>
       </c>
@@ -863,7 +924,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>22</v>
       </c>
@@ -871,7 +932,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>23</v>
       </c>
@@ -882,7 +943,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>24</v>
       </c>
@@ -890,7 +951,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>25</v>
       </c>
@@ -901,7 +962,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>26</v>
       </c>
@@ -912,7 +973,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>27</v>
       </c>
@@ -923,7 +984,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>28</v>
       </c>
@@ -934,7 +995,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>29</v>
       </c>
@@ -945,7 +1006,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>30</v>
       </c>
@@ -956,7 +1017,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>31</v>
       </c>
@@ -970,7 +1031,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>32</v>
       </c>
@@ -984,7 +1045,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>33</v>
       </c>
@@ -998,7 +1059,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>34</v>
       </c>
@@ -1012,7 +1073,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>35</v>
       </c>
@@ -1026,7 +1087,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>36</v>
       </c>
@@ -1040,7 +1101,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>37</v>
       </c>
@@ -1048,7 +1109,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>38</v>
       </c>
@@ -1059,7 +1120,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>39</v>
       </c>
@@ -1070,7 +1131,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>40</v>
       </c>
@@ -1078,7 +1139,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>41</v>
       </c>
@@ -1086,7 +1147,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>42</v>
       </c>
@@ -1094,7 +1155,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>43</v>
       </c>
@@ -1102,7 +1163,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>44</v>
       </c>
@@ -1110,7 +1171,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>45</v>
       </c>
@@ -1118,7 +1179,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A48">
         <v>46</v>
       </c>
@@ -1126,7 +1187,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A49">
         <v>47</v>
       </c>
@@ -1134,7 +1195,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A50">
         <v>48</v>
       </c>
@@ -1142,7 +1203,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A51">
         <v>49</v>
       </c>
@@ -1150,7 +1211,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A52">
         <v>50</v>
       </c>
@@ -1158,7 +1219,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A53">
         <v>51</v>
       </c>
@@ -1166,7 +1227,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A54">
         <v>52</v>
       </c>
@@ -1177,7 +1238,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A55">
         <v>53</v>
       </c>
@@ -1188,7 +1249,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A56">
         <v>54</v>
       </c>
@@ -1196,7 +1257,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A57">
         <v>55</v>
       </c>
@@ -1207,7 +1268,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A58">
         <v>56</v>
       </c>
@@ -1218,7 +1279,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A59">
         <v>57</v>
       </c>
@@ -1226,7 +1287,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A60">
         <v>58</v>
       </c>
@@ -1237,7 +1298,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A61">
         <v>59</v>
       </c>
@@ -1248,7 +1309,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A62">
         <v>60</v>
       </c>
@@ -1256,7 +1317,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A63">
         <v>61</v>
       </c>
@@ -1264,7 +1325,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A64">
         <v>62</v>
       </c>
@@ -1272,7 +1333,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A65">
         <v>63</v>
       </c>
@@ -1280,7 +1341,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A66">
         <v>64</v>
       </c>
@@ -1288,7 +1349,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A67">
         <v>65</v>
       </c>
@@ -1296,7 +1357,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A68">
         <v>66</v>
       </c>
@@ -1304,7 +1365,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A69">
         <v>67</v>
       </c>
@@ -1312,7 +1373,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A70">
         <v>68</v>
       </c>
@@ -1320,7 +1381,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A71">
         <v>69</v>
       </c>
@@ -1328,7 +1389,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A72">
         <v>70</v>
       </c>
@@ -1336,7 +1397,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A73">
         <v>71</v>
       </c>
@@ -1344,7 +1405,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A74">
         <v>72</v>
       </c>
@@ -1355,7 +1416,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A75">
         <v>73</v>
       </c>
@@ -1366,7 +1427,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A76">
         <v>74</v>
       </c>
@@ -1374,7 +1435,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A77">
         <v>75</v>
       </c>
@@ -1385,7 +1446,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A78">
         <v>76</v>
       </c>
@@ -1396,7 +1457,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A79">
         <v>77</v>
       </c>
@@ -1404,7 +1465,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A80">
         <v>78</v>
       </c>
@@ -1412,7 +1473,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A81">
         <v>79</v>
       </c>
@@ -1420,7 +1481,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A82">
         <v>80</v>
       </c>
@@ -1428,7 +1489,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A83">
         <v>81</v>
       </c>
@@ -1436,7 +1497,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A84">
         <v>82</v>
       </c>
@@ -1444,7 +1505,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A85">
         <v>83</v>
       </c>
@@ -1452,7 +1513,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A86">
         <v>84</v>
       </c>
@@ -1460,7 +1521,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A87">
         <v>85</v>
       </c>
@@ -1478,18 +1539,18 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD4AB989-1152-4CA5-8448-1A785E215488}">
   <dimension ref="A1:D128"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="2" width="15.28515625" customWidth="1"/>
-    <col min="3" max="3" width="15.140625" customWidth="1"/>
-    <col min="4" max="4" width="51.7109375" customWidth="1"/>
-    <col min="17" max="17" width="8.85546875" customWidth="1"/>
+    <col min="1" max="2" width="15.26953125" customWidth="1"/>
+    <col min="3" max="3" width="15.1796875" customWidth="1"/>
+    <col min="4" max="4" width="51.7265625" customWidth="1"/>
+    <col min="17" max="17" width="8.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
@@ -1503,7 +1564,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>0</v>
       </c>
@@ -1514,7 +1575,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>1</v>
       </c>
@@ -1525,7 +1586,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>2</v>
       </c>
@@ -1539,7 +1600,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>3</v>
       </c>
@@ -1550,7 +1611,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>4</v>
       </c>
@@ -1561,7 +1622,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>5</v>
       </c>
@@ -1572,7 +1633,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>6</v>
       </c>
@@ -1583,7 +1644,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>7</v>
       </c>
@@ -1594,7 +1655,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>8</v>
       </c>
@@ -1608,7 +1669,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>9</v>
       </c>
@@ -1622,7 +1683,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>10</v>
       </c>
@@ -1630,7 +1691,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>11</v>
       </c>
@@ -1638,7 +1699,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>12</v>
       </c>
@@ -1649,7 +1710,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>13</v>
       </c>
@@ -1657,7 +1718,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>14</v>
       </c>
@@ -1668,7 +1729,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>15</v>
       </c>
@@ -1676,7 +1737,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>16</v>
       </c>
@@ -1684,7 +1745,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>17</v>
       </c>
@@ -1692,7 +1753,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>18</v>
       </c>
@@ -1700,7 +1761,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>19</v>
       </c>
@@ -1708,7 +1769,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>20</v>
       </c>
@@ -1716,7 +1777,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>21</v>
       </c>
@@ -1724,7 +1785,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>22</v>
       </c>
@@ -1732,7 +1793,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>23</v>
       </c>
@@ -1746,7 +1807,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>24</v>
       </c>
@@ -1757,7 +1818,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>25</v>
       </c>
@@ -1765,7 +1826,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>26</v>
       </c>
@@ -1779,7 +1840,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>27</v>
       </c>
@@ -1790,7 +1851,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>28</v>
       </c>
@@ -1804,7 +1865,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>29</v>
       </c>
@@ -1818,7 +1879,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>30</v>
       </c>
@@ -1829,7 +1890,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>31</v>
       </c>
@@ -1840,7 +1901,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>32</v>
       </c>
@@ -1848,7 +1909,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>33</v>
       </c>
@@ -1859,7 +1920,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>34</v>
       </c>
@@ -1867,7 +1928,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>35</v>
       </c>
@@ -1878,7 +1939,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>36</v>
       </c>
@@ -1889,7 +1950,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>37</v>
       </c>
@@ -1897,7 +1958,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>38</v>
       </c>
@@ -1908,7 +1969,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>39</v>
       </c>
@@ -1916,7 +1977,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>40</v>
       </c>
@@ -1930,7 +1991,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>41</v>
       </c>
@@ -1944,7 +2005,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>42</v>
       </c>
@@ -1952,7 +2013,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>43</v>
       </c>
@@ -1966,7 +2027,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>44</v>
       </c>
@@ -1977,7 +2038,7 @@
         <v>0.45</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>45</v>
       </c>
@@ -1988,7 +2049,7 @@
         <v>0.45</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A48">
         <v>46</v>
       </c>
@@ -2002,7 +2063,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A49">
         <v>47</v>
       </c>
@@ -2013,7 +2074,7 @@
         <v>0.45</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A50">
         <v>48</v>
       </c>
@@ -2024,7 +2085,7 @@
         <v>0.45</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A51">
         <v>49</v>
       </c>
@@ -2035,7 +2096,7 @@
         <v>0.45</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A52">
         <v>50</v>
       </c>
@@ -2049,7 +2110,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A53">
         <v>51</v>
       </c>
@@ -2060,7 +2121,7 @@
         <v>0.45</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A54">
         <v>52</v>
       </c>
@@ -2071,7 +2132,7 @@
         <v>0.45</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A55">
         <v>53</v>
       </c>
@@ -2082,7 +2143,7 @@
         <v>0.45</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A56">
         <v>54</v>
       </c>
@@ -2096,7 +2157,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A57">
         <v>55</v>
       </c>
@@ -2107,7 +2168,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A58">
         <v>56</v>
       </c>
@@ -2118,7 +2179,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A59">
         <v>57</v>
       </c>
@@ -2129,7 +2190,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A60">
         <v>58</v>
       </c>
@@ -2143,7 +2204,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A61">
         <v>59</v>
       </c>
@@ -2154,7 +2215,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A62">
         <v>60</v>
       </c>
@@ -2165,7 +2226,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A63">
         <v>61</v>
       </c>
@@ -2176,7 +2237,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A64">
         <v>62</v>
       </c>
@@ -2190,7 +2251,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A65">
         <v>63</v>
       </c>
@@ -2201,7 +2262,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A66">
         <v>64</v>
       </c>
@@ -2209,7 +2270,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A67">
         <v>65</v>
       </c>
@@ -2217,7 +2278,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A68">
         <v>66</v>
       </c>
@@ -2225,7 +2286,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A69">
         <v>67</v>
       </c>
@@ -2233,7 +2294,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A70">
         <v>68</v>
       </c>
@@ -2247,7 +2308,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A71">
         <v>69</v>
       </c>
@@ -2255,7 +2316,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A72">
         <v>70</v>
       </c>
@@ -2263,7 +2324,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A73">
         <v>71</v>
       </c>
@@ -2271,7 +2332,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A74">
         <v>72</v>
       </c>
@@ -2279,7 +2340,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A75">
         <v>73</v>
       </c>
@@ -2287,7 +2348,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A76">
         <v>74</v>
       </c>
@@ -2295,7 +2356,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A77">
         <v>75</v>
       </c>
@@ -2303,7 +2364,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A78">
         <v>76</v>
       </c>
@@ -2311,7 +2372,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A79">
         <v>77</v>
       </c>
@@ -2319,7 +2380,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A80">
         <v>78</v>
       </c>
@@ -2327,7 +2388,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A81">
         <v>79</v>
       </c>
@@ -2335,7 +2396,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A82">
         <v>80</v>
       </c>
@@ -2343,7 +2404,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A83">
         <v>81</v>
       </c>
@@ -2351,7 +2412,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A84">
         <v>82</v>
       </c>
@@ -2359,7 +2420,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A85">
         <v>83</v>
       </c>
@@ -2367,7 +2428,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A86">
         <v>84</v>
       </c>
@@ -2375,7 +2436,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A87">
         <v>85</v>
       </c>
@@ -2383,7 +2444,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A88">
         <v>86</v>
       </c>
@@ -2391,7 +2452,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A89">
         <v>87</v>
       </c>
@@ -2399,7 +2460,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A90">
         <v>88</v>
       </c>
@@ -2407,7 +2468,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A91">
         <v>89</v>
       </c>
@@ -2415,7 +2476,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A92">
         <v>90</v>
       </c>
@@ -2423,7 +2484,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A93">
         <v>91</v>
       </c>
@@ -2431,7 +2492,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A94">
         <v>92</v>
       </c>
@@ -2439,7 +2500,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A95">
         <v>93</v>
       </c>
@@ -2447,7 +2508,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A96">
         <v>94</v>
       </c>
@@ -2455,7 +2516,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A97">
         <v>95</v>
       </c>
@@ -2463,7 +2524,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A98">
         <v>96</v>
       </c>
@@ -2471,7 +2532,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A99">
         <v>97</v>
       </c>
@@ -2479,7 +2540,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A100">
         <v>98</v>
       </c>
@@ -2487,7 +2548,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A101">
         <v>99</v>
       </c>
@@ -2495,7 +2556,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A102">
         <v>100</v>
       </c>
@@ -2503,7 +2564,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A103">
         <v>101</v>
       </c>
@@ -2511,7 +2572,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A104">
         <v>102</v>
       </c>
@@ -2519,7 +2580,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A105">
         <v>103</v>
       </c>
@@ -2527,7 +2588,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A106">
         <v>104</v>
       </c>
@@ -2535,7 +2596,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A107">
         <v>105</v>
       </c>
@@ -2543,7 +2604,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A108">
         <v>106</v>
       </c>
@@ -2551,7 +2612,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A109">
         <v>107</v>
       </c>
@@ -2559,7 +2620,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A110">
         <v>108</v>
       </c>
@@ -2567,7 +2628,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A111">
         <v>109</v>
       </c>
@@ -2575,7 +2636,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A112">
         <v>110</v>
       </c>
@@ -2583,7 +2644,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A113">
         <v>111</v>
       </c>
@@ -2591,7 +2652,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A114">
         <v>112</v>
       </c>
@@ -2599,7 +2660,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A115">
         <v>113</v>
       </c>
@@ -2607,7 +2668,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A116">
         <v>114</v>
       </c>
@@ -2615,7 +2676,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A117">
         <v>115</v>
       </c>
@@ -2623,7 +2684,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A118">
         <v>116</v>
       </c>
@@ -2631,7 +2692,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A119">
         <v>117</v>
       </c>
@@ -2639,7 +2700,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A120">
         <v>118</v>
       </c>
@@ -2647,7 +2708,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="121" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A121">
         <v>119</v>
       </c>
@@ -2655,7 +2716,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="122" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A122">
         <v>120</v>
       </c>
@@ -2663,7 +2724,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="123" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A123">
         <v>121</v>
       </c>
@@ -2671,7 +2732,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="124" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A124">
         <v>122</v>
       </c>
@@ -2679,7 +2740,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="125" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A125">
         <v>123</v>
       </c>
@@ -2687,7 +2748,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="126" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A126">
         <v>124</v>
       </c>
@@ -2695,7 +2756,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="127" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A127">
         <v>125</v>
       </c>
@@ -2703,7 +2764,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="128" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A128">
         <v>126</v>
       </c>
